--- a/hand/attachment/wuji-hand-rl-open-source-base/BOM.xlsx
+++ b/hand/attachment/wuji-hand-rl-open-source-base/BOM.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\13265\Downloads\Wuji Hand-RL Open-Source Fixture-B\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:81_{480DC972-B146-44AB-8959-07D9A4D390E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -336,17 +334,17 @@
 
 <file path=xl/revisions/revisionHeaders.xml><?xml version="1.0" encoding="utf-8"?>
 <headers xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac" guid="{674D077F-5884-4546-A0BC-E6E9553DD916}" diskRevisions="1" revisionId="14" version="3">
-  <header guid="{8C92BF5E-A7B6-4466-8460-AECF80CBC2AC}" dateTime="2026-05-26T17:10:44" maxSheetId="2" userName="rong yi" r:id="rId1">
+  <header guid="{8C92BF5E-A7B6-4466-8460-AECF80CBC2AC}" dateTime="2026-05-26T17:10:44" maxSheetId="2" userName="" r:id="rId1">
     <sheetIdMap count="1">
       <sheetId val="1"/>
     </sheetIdMap>
   </header>
-  <header guid="{9DBB4C9A-F20E-4891-ADE4-47B8D13E0973}" dateTime="2026-06-03T16:03:11" maxSheetId="2" userName="rong yi" r:id="rId2" minRId="1" maxRId="2">
+  <header guid="{9DBB4C9A-F20E-4891-ADE4-47B8D13E0973}" dateTime="2026-06-03T16:03:11" maxSheetId="2" userName="" r:id="rId2" minRId="1" maxRId="2">
     <sheetIdMap count="1">
       <sheetId val="1"/>
     </sheetIdMap>
   </header>
-  <header guid="{674D077F-5884-4546-A0BC-E6E9553DD916}" dateTime="2026-06-05T19:34:52" maxSheetId="2" userName="rong yi" r:id="rId3" minRId="3" maxRId="14">
+  <header guid="{674D077F-5884-4546-A0BC-E6E9553DD916}" dateTime="2026-06-05T19:34:52" maxSheetId="2" userName="" r:id="rId3" minRId="3" maxRId="14">
     <sheetIdMap count="1">
       <sheetId val="1"/>
     </sheetIdMap>
@@ -1006,7 +1004,7 @@
   </customSheetViews>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>